--- a/task5/EXAM-test-answer.xlsx
+++ b/task5/EXAM-test-answer.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\husey\Desktop\pjatk 2. semester\rbd\task5\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D48F4070-0A01-4590-A544-43606B53D749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{249EA7EF-4119-4123-AE63-15CC5D1D7BCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{B25DCD79-F0C2-4DF3-9A93-68E160D71636}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="51">
   <si>
     <t>BCNF</t>
   </si>
@@ -186,6 +186,9 @@
   </si>
   <si>
     <t>E,A,B</t>
+  </si>
+  <si>
+    <t>K4 = D,E,B</t>
   </si>
 </sst>
 </file>
@@ -273,7 +276,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -287,12 +290,11 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -688,7 +690,7 @@
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
+      <c r="A7" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B7" t="s">
@@ -705,13 +707,13 @@
       <c r="H8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I8" s="8" t="s">
-        <v>14</v>
+      <c r="I8" s="11" t="s">
+        <v>13</v>
       </c>
       <c r="J8" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K8" s="9" t="s">
+      <c r="K8" s="7" t="s">
         <v>13</v>
       </c>
     </row>
@@ -731,22 +733,22 @@
       <c r="J9" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="K9" s="9" t="s">
+      <c r="K9" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="11"/>
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-      <c r="F13" s="11"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="11"/>
-      <c r="I13" s="11"/>
-      <c r="J13" s="11"/>
-      <c r="K13" s="11"/>
+      <c r="A13" s="10"/>
+      <c r="B13" s="10"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="10"/>
+      <c r="H13" s="10"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="10"/>
+      <c r="K13" s="10"/>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -819,7 +821,7 @@
       <c r="H22" t="s">
         <v>13</v>
       </c>
-      <c r="I22" s="10" t="s">
+      <c r="I22" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J22" t="s">
@@ -827,10 +829,10 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="10" t="s">
+      <c r="A23" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B23" s="12" t="s">
+      <c r="B23" t="s">
         <v>1</v>
       </c>
       <c r="F23" t="s">
@@ -839,13 +841,13 @@
       <c r="G23" t="s">
         <v>13</v>
       </c>
-      <c r="H23" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I23" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J23" s="10" t="s">
+      <c r="H23" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I23" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J23" s="9" t="s">
         <v>14</v>
       </c>
     </row>
@@ -859,7 +861,7 @@
       <c r="H24" t="s">
         <v>13</v>
       </c>
-      <c r="I24" s="10" t="s">
+      <c r="I24" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J24" t="s">
@@ -867,17 +869,17 @@
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
-      <c r="K30" s="11"/>
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
+      <c r="K30" s="10"/>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
@@ -927,7 +929,7 @@
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="10" t="s">
+      <c r="A39" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B39" t="s">
@@ -941,13 +943,13 @@
       <c r="G40" t="s">
         <v>13</v>
       </c>
-      <c r="H40" s="10" t="s">
+      <c r="H40" s="9" t="s">
         <v>14</v>
       </c>
       <c r="I40" t="s">
         <v>13</v>
       </c>
-      <c r="J40" s="10" t="s">
+      <c r="J40" s="9" t="s">
         <v>14</v>
       </c>
     </row>
@@ -964,7 +966,7 @@
       <c r="I41" t="s">
         <v>13</v>
       </c>
-      <c r="J41" s="10" t="s">
+      <c r="J41" s="9" t="s">
         <v>14</v>
       </c>
     </row>
@@ -975,13 +977,13 @@
       <c r="G42" t="s">
         <v>13</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H42" s="9" t="s">
         <v>14</v>
       </c>
       <c r="I42" t="s">
         <v>13</v>
       </c>
-      <c r="J42" s="10" t="s">
+      <c r="J42" s="9" t="s">
         <v>14</v>
       </c>
     </row>
@@ -998,22 +1000,22 @@
       <c r="I43" t="s">
         <v>13</v>
       </c>
-      <c r="J43" s="10" t="s">
+      <c r="J43" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="11"/>
-      <c r="B48" s="11"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="11"/>
-      <c r="G48" s="11"/>
-      <c r="H48" s="11"/>
-      <c r="I48" s="11"/>
-      <c r="J48" s="11"/>
-      <c r="K48" s="11"/>
+      <c r="A48" s="10"/>
+      <c r="B48" s="10"/>
+      <c r="C48" s="10"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10"/>
+      <c r="F48" s="10"/>
+      <c r="G48" s="10"/>
+      <c r="H48" s="10"/>
+      <c r="I48" s="10"/>
+      <c r="J48" s="10"/>
+      <c r="K48" s="10"/>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
@@ -1077,29 +1079,29 @@
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>12</v>
+      </c>
       <c r="F56" t="s">
         <v>25</v>
       </c>
       <c r="G56" t="s">
         <v>13</v>
       </c>
-      <c r="H56" s="10" t="s">
+      <c r="H56" s="9" t="s">
         <v>14</v>
       </c>
       <c r="I56" t="s">
         <v>13</v>
       </c>
-      <c r="J56" s="10" t="s">
+      <c r="J56" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="10" t="s">
-        <v>15</v>
-      </c>
-      <c r="B57" s="12" t="s">
-        <v>1</v>
-      </c>
       <c r="F57" t="s">
         <v>26</v>
       </c>
@@ -1109,7 +1111,7 @@
       <c r="H57" t="s">
         <v>13</v>
       </c>
-      <c r="I57" s="10" t="s">
+      <c r="I57" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J57" t="s">
@@ -1117,19 +1119,25 @@
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1</v>
+      </c>
       <c r="F58" t="s">
         <v>27</v>
       </c>
       <c r="G58" t="s">
         <v>13</v>
       </c>
-      <c r="H58" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I58" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J58" s="10" t="s">
+      <c r="H58" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I58" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J58" s="9" t="s">
         <v>14</v>
       </c>
     </row>
@@ -1143,7 +1151,7 @@
       <c r="H59" t="s">
         <v>13</v>
       </c>
-      <c r="I59" s="10" t="s">
+      <c r="I59" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J59" t="s">
@@ -1160,25 +1168,25 @@
       <c r="H60" t="s">
         <v>13</v>
       </c>
-      <c r="I60" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J60" s="10" t="s">
+      <c r="I60" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J60" s="9" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A65" s="11"/>
-      <c r="B65" s="11"/>
-      <c r="C65" s="11"/>
-      <c r="D65" s="11"/>
-      <c r="E65" s="11"/>
-      <c r="F65" s="11"/>
-      <c r="G65" s="11"/>
-      <c r="H65" s="11"/>
-      <c r="I65" s="11"/>
-      <c r="J65" s="11"/>
-      <c r="K65" s="11"/>
+      <c r="A65" s="10"/>
+      <c r="B65" s="10"/>
+      <c r="C65" s="10"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10"/>
+      <c r="F65" s="10"/>
+      <c r="G65" s="10"/>
+      <c r="H65" s="10"/>
+      <c r="I65" s="10"/>
+      <c r="J65" s="10"/>
+      <c r="K65" s="10"/>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
@@ -1234,7 +1242,7 @@
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A73" s="10" t="s">
+      <c r="A73" s="9" t="s">
         <v>15</v>
       </c>
       <c r="B73" t="s">
@@ -1269,7 +1277,7 @@
       <c r="H74" t="s">
         <v>13</v>
       </c>
-      <c r="I74" s="10" t="s">
+      <c r="I74" s="9" t="s">
         <v>14</v>
       </c>
       <c r="J74" t="s">
@@ -1283,16 +1291,15 @@
       <c r="G75" t="s">
         <v>13</v>
       </c>
-      <c r="H75" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="I75" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="J75" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="K75" s="12"/>
+      <c r="H75" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I75" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="J75" s="9" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
       <c r="F76" t="s">
@@ -1315,17 +1322,17 @@
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A79" s="11"/>
-      <c r="B79" s="11"/>
-      <c r="C79" s="11"/>
-      <c r="D79" s="11"/>
-      <c r="E79" s="11"/>
-      <c r="F79" s="11"/>
-      <c r="G79" s="11"/>
-      <c r="H79" s="11"/>
-      <c r="I79" s="11"/>
-      <c r="J79" s="11"/>
-      <c r="K79" s="11"/>
+      <c r="A79" s="10"/>
+      <c r="B79" s="10"/>
+      <c r="C79" s="10"/>
+      <c r="D79" s="10"/>
+      <c r="E79" s="10"/>
+      <c r="F79" s="10"/>
+      <c r="G79" s="10"/>
+      <c r="H79" s="10"/>
+      <c r="I79" s="10"/>
+      <c r="J79" s="10"/>
+      <c r="K79" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
